--- a/Side Bar Files/GWD Data/HP Erection and Pullout.xlsx
+++ b/Side Bar Files/GWD Data/HP Erection and Pullout.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="28">
   <si>
     <t>Hand Pump Erection and Pullout</t>
   </si>
@@ -93,6 +93,12 @@
   </si>
   <si>
     <t>Hand pump pullout (extra deep well)</t>
+  </si>
+  <si>
+    <t>Hand pump pullout and re-erection (deep well)</t>
+  </si>
+  <si>
+    <t>Hand pump pullout and re-erection (extra deep well)</t>
   </si>
 </sst>
 </file>
@@ -244,32 +250,18 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -353,16 +345,49 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -739,8 +764,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{137E97DF-F7BC-4FCA-8A6A-61C36BE1B9A7}">
-  <dimension ref="A1:F45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA9C8305-C98A-40FE-B372-FD2635F9BAA6}">
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1" spans="1:6" ht="12.75">
@@ -1431,8 +1456,346 @@
       <c r="E45" s="6"/>
       <c r="F45" s="7"/>
     </row>
+    <row r="46" spans="1:6" ht="12.75">
+      <c r="A46" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="7"/>
+    </row>
+    <row r="47" spans="1:6" ht="12.75">
+      <c r="A47" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="12.75">
+      <c r="A48" s="10"/>
+      <c r="B48" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="12">
+        <v>0.10</v>
+      </c>
+      <c r="E48" s="12">
+        <v>3000</v>
+      </c>
+      <c r="F48" s="13">
+        <f>D48*E48</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="12.75">
+      <c r="A49" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" s="12">
+        <v>2</v>
+      </c>
+      <c r="E49" s="12">
+        <v>784</v>
+      </c>
+      <c r="F49" s="13">
+        <f>D49*E49</f>
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="12.75">
+      <c r="A50" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="12">
+        <v>3.50</v>
+      </c>
+      <c r="E50" s="12">
+        <v>645</v>
+      </c>
+      <c r="F50" s="13">
+        <f>D50*E50</f>
+        <v>2257.50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="12.75">
+      <c r="A51" s="14"/>
+      <c r="B51" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="13">
+        <f>SUM(F48:F50)</f>
+        <v>4125.50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="12.75">
+      <c r="A52" s="14"/>
+      <c r="B52" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="13">
+        <f>F51*0.01</f>
+        <v>41.255</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="12.75">
+      <c r="A53" s="14"/>
+      <c r="B53" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="13">
+        <f>SUM(F51:F52)</f>
+        <v>4166.7550000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="12.75">
+      <c r="A54" s="14"/>
+      <c r="B54" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="13">
+        <f>F53*0.15</f>
+        <v>625.01324999999997</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="12.75">
+      <c r="A55" s="14"/>
+      <c r="B55" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="13">
+        <f>MROUND(SUM(F53:F54),1)</f>
+        <v>4792</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="12.75">
+      <c r="A56" s="28" t="str">
+        <f>CONCATENATE("Say Rs (",F55," x Cost Index)")</f>
+        <v>Say Rs (4792 x Cost Index)</v>
+      </c>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="7"/>
+    </row>
+    <row r="57" spans="1:6" ht="12.75">
+      <c r="A57" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B57" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="7"/>
+    </row>
+    <row r="58" spans="1:6" ht="12.75">
+      <c r="A58" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="B58" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C58" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="E58" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="F58" s="32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="12.75">
+      <c r="A59" s="33"/>
+      <c r="B59" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C59" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="D59" s="35">
+        <v>0.20</v>
+      </c>
+      <c r="E59" s="35">
+        <v>3000</v>
+      </c>
+      <c r="F59" s="36">
+        <f>D59*E59</f>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="12.75">
+      <c r="A60" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C60" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="35">
+        <v>2.50</v>
+      </c>
+      <c r="E60" s="35">
+        <v>784</v>
+      </c>
+      <c r="F60" s="36">
+        <f>D60*E60</f>
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="12.75">
+      <c r="A61" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B61" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="C61" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="35">
+        <v>4</v>
+      </c>
+      <c r="E61" s="35">
+        <v>645</v>
+      </c>
+      <c r="F61" s="36">
+        <f>D61*E61</f>
+        <v>2580</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="12.75">
+      <c r="A62" s="37"/>
+      <c r="B62" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="36">
+        <f>SUM(F59:F61)</f>
+        <v>5140</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="12.75">
+      <c r="A63" s="37"/>
+      <c r="B63" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="36">
+        <f>F62*0.01</f>
+        <v>51.40</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="12.75">
+      <c r="A64" s="37"/>
+      <c r="B64" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" s="6"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="36">
+        <f>SUM(F62:F63)</f>
+        <v>5191.40</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="12.75">
+      <c r="A65" s="37"/>
+      <c r="B65" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="36">
+        <f>F64*0.15</f>
+        <v>778.71</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="12.75">
+      <c r="A66" s="37"/>
+      <c r="B66" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="36">
+        <f>MROUND(SUM(F64:F65),1)</f>
+        <v>5970</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="12.75">
+      <c r="A67" s="39" t="str">
+        <f>CONCATENATE("Say Rs (",F66," x Cost Index)")</f>
+        <v>Say Rs (5970 x Cost Index)</v>
+      </c>
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="43">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B7:E7"/>
@@ -1447,6 +1810,13 @@
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="B22:E22"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B33:E33"/>
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="B40:E40"/>
@@ -1454,14 +1824,21 @@
     <mergeCell ref="B42:E42"/>
     <mergeCell ref="B43:E43"/>
     <mergeCell ref="B44:E44"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="B64:E64"/>
+    <mergeCell ref="B65:E65"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="A67:F67"/>
     <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B55:E55"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Side Bar Files/GWD Data/HP Erection and Pullout.xlsx
+++ b/Side Bar Files/GWD Data/HP Erection and Pullout.xlsx
@@ -764,7 +764,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA9C8305-C98A-40FE-B372-FD2635F9BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C94C9862-E8B4-4F5A-941C-2FEAA7D2BAA6}">
   <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/HP Erection and Pullout.xlsx
+++ b/Side Bar Files/GWD Data/HP Erection and Pullout.xlsx
@@ -764,7 +764,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C94C9862-E8B4-4F5A-941C-2FEAA7D2BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AF777E8-D595-43E3-9B7B-832EC71CBAA6}">
   <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
